--- a/ProjectDB.xlsx
+++ b/ProjectDB.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nass0\OneDrive\바탕 화면\Projects\2026_01_2_B_GameProjcect\"/>
@@ -535,6 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B20CCA1-817C-4E28-9353-F24032DFAC4A}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
